--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.86241732308663</v>
+        <v>11.51514281500158</v>
       </c>
       <c r="D2" t="n">
-        <v>50.26184523492697</v>
+        <v>8.167549850675634</v>
       </c>
       <c r="E2" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F2" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.52185142981902</v>
+        <v>10.80980085734559</v>
       </c>
       <c r="D3" t="n">
-        <v>55.88713541085524</v>
+        <v>9.081659504263978</v>
       </c>
       <c r="E3" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F3" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.46749374016352</v>
+        <v>10.47596773277657</v>
       </c>
       <c r="D4" t="n">
-        <v>58.57687256929991</v>
+        <v>9.518741792511236</v>
       </c>
       <c r="E4" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F4" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.29921850009255</v>
+        <v>9.31112300626504</v>
       </c>
       <c r="D5" t="n">
-        <v>20.12451168117133</v>
+        <v>3.270233148190342</v>
       </c>
       <c r="E5" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F5" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.27846539293758</v>
+        <v>9.307750626352357</v>
       </c>
       <c r="D6" t="n">
-        <v>17.32772345116346</v>
+        <v>2.815755060814062</v>
       </c>
       <c r="E6" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F6" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.22187035422535</v>
+        <v>8.16105393256162</v>
       </c>
       <c r="D7" t="n">
-        <v>50.18823406725561</v>
+        <v>8.155588035929036</v>
       </c>
       <c r="E7" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F7" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>55.83811837650783</v>
+        <v>9.073694236182522</v>
       </c>
       <c r="D8" t="n">
-        <v>55.52679510682941</v>
+        <v>9.023104204859779</v>
       </c>
       <c r="E8" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F8" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.2574041972369</v>
+        <v>4.754328182050996</v>
       </c>
       <c r="D9" t="n">
-        <v>10.97724920005007</v>
+        <v>1.783802995008137</v>
       </c>
       <c r="E9" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F9" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>56.85163931445182</v>
+        <v>9.238391388598421</v>
       </c>
       <c r="D10" t="n">
-        <v>23.28626204439004</v>
+        <v>3.784017582213381</v>
       </c>
       <c r="E10" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F10" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.80388719711596</v>
+        <v>9.068131669531343</v>
       </c>
       <c r="D11" t="n">
-        <v>31.00403199585499</v>
+        <v>5.038155199326436</v>
       </c>
       <c r="E11" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F11" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>50.4002631794652</v>
+        <v>8.190042766663096</v>
       </c>
       <c r="D12" t="n">
-        <v>46.80873055569685</v>
+        <v>7.606418715300738</v>
       </c>
       <c r="E12" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F12" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>57.14086817942241</v>
+        <v>9.285391079156142</v>
       </c>
       <c r="D13" t="n">
-        <v>56.85914024802888</v>
+        <v>9.239610290304693</v>
       </c>
       <c r="E13" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F13" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>60.79756685662804</v>
+        <v>9.879604614202057</v>
       </c>
       <c r="D14" t="n">
-        <v>60.13643162737461</v>
+        <v>9.772170139448374</v>
       </c>
       <c r="E14" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F14" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74.2096037547111</v>
+        <v>12.05906061014055</v>
       </c>
       <c r="D15" t="n">
-        <v>73.71650726229046</v>
+        <v>11.9789324301222</v>
       </c>
       <c r="E15" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F15" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>76.24365940925475</v>
+        <v>12.3895946540039</v>
       </c>
       <c r="D16" t="n">
-        <v>75.63186432655795</v>
+        <v>12.29017795306567</v>
       </c>
       <c r="E16" t="n">
-        <v>11.04129290598304</v>
+        <v>1.794210097222244</v>
       </c>
       <c r="F16" t="n">
-        <v>19.67262686111446</v>
+        <v>3.1968018649311</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
